--- a/Analyst Testing XLSX.xlsx
+++ b/Analyst Testing XLSX.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop Trainning\Unconverted Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\urjita\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04793AF-0311-41B7-9D5B-F86DE6C7B05E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="0" windowWidth="15240" windowHeight="8670" tabRatio="926"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="926" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Inputs and Trends" sheetId="35" r:id="rId1"/>
@@ -19,16 +20,29 @@
     <definedName name="Range1">'Data Inputs and Trends'!$G$10:$G$21</definedName>
     <definedName name="Range2">'Data Inputs and Trends'!$B$27:$G$38</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcOnSave="0"/>
+  <calcPr calcId="191029"/>
   <customWorkbookViews>
+    <customWorkbookView name="Teresa Bergholz - Personal View" guid="{0024717D-C410-4ED7-B8ED-7D14D8DF0A53}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1240" windowHeight="861" activeSheetId="12"/>
     <customWorkbookView name="lir - Personal View" guid="{F75E00F2-D522-4EEB-BB05-C5D926A09C2B}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1020" windowHeight="552" activeSheetId="5"/>
-    <customWorkbookView name="Teresa Bergholz - Personal View" guid="{0024717D-C410-4ED7-B8ED-7D14D8DF0A53}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1240" windowHeight="861" activeSheetId="12"/>
   </customWorkbookViews>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="28">
   <si>
     <t>QC Lab Sample Assay Spreadsheet</t>
   </si>
@@ -117,7 +131,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode=";;;"/>
   </numFmts>
@@ -233,7 +247,7 @@
       <charset val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -276,12 +290,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="36">
     <border>
@@ -751,7 +759,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -801,32 +809,29 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
@@ -1013,13 +1018,6 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
@@ -1054,7 +1052,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1424,7 +1422,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:O49"/>
   <sheetFormatPr defaultColWidth="13.140625" defaultRowHeight="15"/>
@@ -1437,15 +1435,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="41.25" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:15" ht="15" customHeight="1">
@@ -1539,17 +1537,17 @@
       <c r="O7" s="15"/>
     </row>
     <row r="8" spans="1:15" ht="15.6" customHeight="1">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="76"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="76"/>
-      <c r="F8" s="76"/>
-      <c r="G8" s="77"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="74"/>
       <c r="J8" s="16" t="s">
         <v>6</v>
       </c>
@@ -1559,375 +1557,375 @@
       </c>
       <c r="M8" s="17"/>
       <c r="N8" s="17"/>
-      <c r="O8" s="19"/>
+      <c r="O8" s="15"/>
     </row>
     <row r="9" spans="1:15" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="33">
         <v>1</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="34">
         <v>2</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="34">
         <v>3</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="35">
         <v>4</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="34">
         <v>5</v>
       </c>
-      <c r="G9" s="37">
+      <c r="G9" s="36">
         <v>6</v>
       </c>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
     </row>
     <row r="10" spans="1:15" ht="15.6" customHeight="1">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="20">
         <v>11</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="20">
         <v>12</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="20">
         <f>D11</f>
         <v>45</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="20">
         <v>34</v>
       </c>
-      <c r="F10" s="63">
+      <c r="F10" s="62">
         <v>56</v>
       </c>
-      <c r="G10" s="63">
+      <c r="G10" s="62">
         <v>20</v>
       </c>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
     </row>
     <row r="11" spans="1:15" ht="15.6" customHeight="1">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="23">
         <v>12</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="23">
         <v>14</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="23">
         <v>45</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="23">
         <v>16</v>
       </c>
-      <c r="F11" s="64">
+      <c r="F11" s="63">
         <v>56</v>
       </c>
-      <c r="G11" s="64">
+      <c r="G11" s="63">
         <v>19</v>
       </c>
-      <c r="J11" s="22"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
     </row>
     <row r="12" spans="1:15" ht="15.6" customHeight="1">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="23">
         <v>14</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="23">
         <v>34</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="23">
         <v>22</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="23">
         <v>14</v>
       </c>
-      <c r="F12" s="64">
+      <c r="F12" s="63">
         <v>21</v>
       </c>
-      <c r="G12" s="64">
+      <c r="G12" s="63">
         <v>14</v>
       </c>
-      <c r="J12" s="22"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
     </row>
     <row r="13" spans="1:15" ht="15.6" customHeight="1">
-      <c r="A13" s="33" t="s">
+      <c r="A13" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="23">
         <v>15</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="23">
         <v>15</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="23">
         <v>26</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="23">
         <v>43</v>
       </c>
-      <c r="F13" s="64">
+      <c r="F13" s="63">
         <v>15</v>
       </c>
-      <c r="G13" s="73"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
+      <c r="G13" s="70"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
     </row>
     <row r="14" spans="1:15" ht="15.6" customHeight="1">
-      <c r="A14" s="33" t="s">
+      <c r="A14" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24">
+      <c r="B14" s="23"/>
+      <c r="C14" s="23">
         <v>17</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="23">
         <v>17</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="23">
         <v>18</v>
       </c>
-      <c r="F14" s="64">
+      <c r="F14" s="63">
         <v>35</v>
       </c>
-      <c r="G14" s="64">
+      <c r="G14" s="63">
         <v>17</v>
       </c>
-      <c r="J14" s="22"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
     </row>
     <row r="15" spans="1:15" ht="15.6" customHeight="1">
-      <c r="A15" s="33" t="s">
+      <c r="A15" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="23">
         <v>19</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="23">
         <v>33</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="23">
         <v>45</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="23">
         <v>19</v>
       </c>
-      <c r="F15" s="64">
+      <c r="F15" s="63">
         <f>SUM(F10:F11)</f>
         <v>112</v>
       </c>
-      <c r="G15" s="64">
+      <c r="G15" s="63">
         <v>11</v>
       </c>
-      <c r="J15" s="22"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
     </row>
     <row r="16" spans="1:15" ht="15.6" customHeight="1">
-      <c r="A16" s="33" t="s">
+      <c r="A16" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24">
+      <c r="B16" s="23"/>
+      <c r="C16" s="23">
         <v>22</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="23">
         <v>32</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="23">
         <v>22</v>
       </c>
-      <c r="F16" s="64">
+      <c r="F16" s="63">
         <v>21</v>
       </c>
-      <c r="G16" s="64">
+      <c r="G16" s="63">
         <v>34</v>
       </c>
-      <c r="J16" s="22"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
     </row>
     <row r="17" spans="1:15" ht="15.6" customHeight="1">
-      <c r="A17" s="33" t="s">
+      <c r="A17" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B17" s="23">
         <v>11</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="23">
         <v>21</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="23">
         <v>36</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="23">
         <v>34</v>
       </c>
-      <c r="F17" s="64">
+      <c r="F17" s="63">
         <v>11</v>
       </c>
-      <c r="G17" s="64">
+      <c r="G17" s="63">
         <v>23</v>
       </c>
-      <c r="J17" s="22"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
     </row>
     <row r="18" spans="1:15" ht="15.6" customHeight="1">
-      <c r="A18" s="33" t="s">
+      <c r="A18" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="24">
+      <c r="B18" s="23">
         <v>19</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="23">
         <v>19</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="23">
         <v>17</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="23">
         <v>19</v>
       </c>
-      <c r="F18" s="64">
+      <c r="F18" s="63">
         <v>11</v>
       </c>
-      <c r="G18" s="64">
+      <c r="G18" s="63">
         <v>56</v>
       </c>
-      <c r="J18" s="22"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
     </row>
     <row r="19" spans="1:15" ht="15.6" customHeight="1">
-      <c r="A19" s="33" t="s">
+      <c r="A19" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24">
+      <c r="B19" s="23"/>
+      <c r="C19" s="23">
         <v>34</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="23">
         <v>23</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="23">
         <v>18</v>
       </c>
-      <c r="F19" s="64">
+      <c r="F19" s="63">
         <v>21</v>
       </c>
-      <c r="G19" s="64">
+      <c r="G19" s="63">
         <v>23</v>
       </c>
-      <c r="J19" s="22"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
     </row>
     <row r="20" spans="1:15" ht="15.6" customHeight="1">
-      <c r="A20" s="33" t="s">
+      <c r="A20" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B20" s="23">
         <v>20</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="23">
         <v>20</v>
       </c>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24">
+      <c r="D20" s="23"/>
+      <c r="E20" s="23">
         <v>20</v>
       </c>
-      <c r="F20" s="64">
+      <c r="F20" s="63">
         <v>22</v>
       </c>
-      <c r="G20" s="64">
+      <c r="G20" s="63">
         <v>20</v>
       </c>
-      <c r="J20" s="22"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
     </row>
     <row r="21" spans="1:15" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A21" s="33" t="s">
+      <c r="A21" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="24">
         <v>21</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="24">
         <v>21</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="24">
         <v>21</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="24">
         <v>21</v>
       </c>
-      <c r="F21" s="65">
+      <c r="F21" s="64">
         <f>SUM(G18:G21)</f>
         <v>110</v>
       </c>
-      <c r="G21" s="65">
+      <c r="G21" s="64">
         <v>11</v>
       </c>
-      <c r="J21" s="22"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
     </row>
     <row r="22" spans="1:15" ht="15.6" customHeight="1">
       <c r="A22" s="3"/>
@@ -1941,476 +1939,476 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="1:15" s="30" customFormat="1" ht="18.75" thickBot="1">
-      <c r="A23" s="26" t="s">
+    <row r="23" spans="1:15" s="29" customFormat="1" ht="18.75" thickBot="1">
+      <c r="A23" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="26"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="25"/>
     </row>
     <row r="24" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1">
-      <c r="A24" s="38"/>
-      <c r="B24" s="78" t="s">
+      <c r="A24" s="37"/>
+      <c r="B24" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="79"/>
-      <c r="D24" s="79"/>
-      <c r="E24" s="79"/>
-      <c r="F24" s="79"/>
-      <c r="G24" s="80"/>
+      <c r="C24" s="76"/>
+      <c r="D24" s="76"/>
+      <c r="E24" s="76"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="77"/>
       <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1">
-      <c r="A25" s="66"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67"/>
-      <c r="F25" s="67"/>
-      <c r="G25" s="68"/>
+      <c r="A25" s="65"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="66"/>
+      <c r="E25" s="66"/>
+      <c r="F25" s="66"/>
+      <c r="G25" s="67"/>
       <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1">
-      <c r="A26" s="39" t="s">
+      <c r="A26" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="40">
+      <c r="B26" s="39">
         <f>B9</f>
         <v>1</v>
       </c>
-      <c r="C26" s="41">
+      <c r="C26" s="40">
         <f>C9</f>
         <v>2</v>
       </c>
-      <c r="D26" s="41">
+      <c r="D26" s="40">
         <f>D9</f>
         <v>3</v>
       </c>
-      <c r="E26" s="41">
+      <c r="E26" s="40">
         <v>4</v>
       </c>
-      <c r="F26" s="41">
+      <c r="F26" s="40">
         <f>F9</f>
         <v>5</v>
       </c>
-      <c r="G26" s="42">
+      <c r="G26" s="41">
         <v>6</v>
       </c>
       <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:15" ht="15.95" customHeight="1">
-      <c r="A27" s="43" t="str">
+      <c r="A27" s="42" t="str">
         <f t="shared" ref="A27:A38" si="0">A10</f>
         <v>Tab 1</v>
       </c>
-      <c r="B27" s="44">
+      <c r="B27" s="43">
         <f>B10*$G$3*$G$4/75</f>
         <v>36.666666666666664</v>
       </c>
-      <c r="C27" s="44">
+      <c r="C27" s="43">
         <v>55</v>
       </c>
-      <c r="D27" s="44">
+      <c r="D27" s="43">
         <f t="shared" ref="D27:D38" si="1">D10*$G$3*$G$4/100</f>
         <v>112.5</v>
       </c>
-      <c r="E27" s="44">
+      <c r="E27" s="43">
         <f>E10*$G$3*$G$4/75</f>
         <v>113.33333333333333</v>
       </c>
-      <c r="F27" s="44">
+      <c r="F27" s="43">
         <f>F10*$G$3*$G$4/200</f>
         <v>70</v>
       </c>
-      <c r="G27" s="45">
+      <c r="G27" s="44">
         <f>G10*$G$3*$G$4/75</f>
         <v>66.666666666666671</v>
       </c>
       <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:15" ht="15.95" customHeight="1">
-      <c r="A28" s="43" t="str">
+      <c r="A28" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tab 2</v>
       </c>
-      <c r="B28" s="44">
+      <c r="B28" s="43">
         <f t="shared" ref="B28:C38" si="2">B11*$G$3*$G$4/100</f>
         <v>30</v>
       </c>
-      <c r="C28" s="44">
+      <c r="C28" s="43">
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="D28" s="44">
+      <c r="D28" s="43">
         <f t="shared" si="1"/>
         <v>112.5</v>
       </c>
-      <c r="E28" s="44">
+      <c r="E28" s="43">
         <f t="shared" ref="E28:G38" si="3">E11*$G$3*$G$4/100</f>
         <v>40</v>
       </c>
-      <c r="F28" s="44">
+      <c r="F28" s="43">
         <f t="shared" si="3"/>
         <v>140</v>
       </c>
-      <c r="G28" s="46">
+      <c r="G28" s="45">
         <f t="shared" si="3"/>
         <v>47.5</v>
       </c>
       <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:15" ht="15.95" customHeight="1">
-      <c r="A29" s="43" t="str">
+      <c r="A29" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tab 3</v>
       </c>
-      <c r="B29" s="44">
+      <c r="B29" s="43">
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="C29" s="44">
+      <c r="C29" s="43">
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
-      <c r="D29" s="44">
+      <c r="D29" s="43">
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
-      <c r="E29" s="44">
+      <c r="E29" s="43">
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="F29" s="44">
+      <c r="F29" s="43">
         <f t="shared" si="3"/>
         <v>52.5</v>
       </c>
-      <c r="G29" s="46">
+      <c r="G29" s="45">
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
       <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:15" ht="15.95" customHeight="1">
-      <c r="A30" s="43" t="str">
+      <c r="A30" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tab 4</v>
       </c>
-      <c r="B30" s="44">
+      <c r="B30" s="43">
         <f t="shared" si="2"/>
         <v>37.5</v>
       </c>
-      <c r="C30" s="44">
+      <c r="C30" s="43">
         <f t="shared" si="2"/>
         <v>37.5</v>
       </c>
-      <c r="D30" s="44">
+      <c r="D30" s="43">
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
-      <c r="E30" s="44">
+      <c r="E30" s="43">
         <f t="shared" si="3"/>
         <v>107.5</v>
       </c>
-      <c r="F30" s="44">
+      <c r="F30" s="43">
         <f t="shared" si="3"/>
         <v>37.5</v>
       </c>
-      <c r="G30" s="46">
+      <c r="G30" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:15" ht="15.95" customHeight="1">
-      <c r="A31" s="43" t="str">
+      <c r="A31" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tab 5</v>
       </c>
-      <c r="B31" s="44">
+      <c r="B31" s="43">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="C31" s="44">
+      <c r="C31" s="43">
         <f t="shared" si="2"/>
         <v>42.5</v>
       </c>
-      <c r="D31" s="44">
+      <c r="D31" s="43">
         <f t="shared" si="1"/>
         <v>42.5</v>
       </c>
-      <c r="E31" s="44">
+      <c r="E31" s="43">
         <f t="shared" si="3"/>
         <v>45</v>
       </c>
-      <c r="F31" s="44">
+      <c r="F31" s="43">
         <f t="shared" si="3"/>
         <v>87.5</v>
       </c>
-      <c r="G31" s="46">
+      <c r="G31" s="45">
         <f t="shared" si="3"/>
         <v>42.5</v>
       </c>
       <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:15" ht="15.95" customHeight="1">
-      <c r="A32" s="43" t="str">
+      <c r="A32" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tab 6</v>
       </c>
-      <c r="B32" s="44">
+      <c r="B32" s="43">
         <f t="shared" si="2"/>
         <v>47.5</v>
       </c>
-      <c r="C32" s="44">
+      <c r="C32" s="43">
         <f t="shared" si="2"/>
         <v>82.5</v>
       </c>
-      <c r="D32" s="44">
+      <c r="D32" s="43">
         <f t="shared" si="1"/>
         <v>112.5</v>
       </c>
-      <c r="E32" s="44">
+      <c r="E32" s="43">
         <f t="shared" si="3"/>
         <v>47.5</v>
       </c>
-      <c r="F32" s="44">
+      <c r="F32" s="43">
         <f t="shared" si="3"/>
         <v>280</v>
       </c>
-      <c r="G32" s="46">
+      <c r="G32" s="45">
         <f t="shared" si="3"/>
         <v>27.5</v>
       </c>
       <c r="H32" s="4"/>
     </row>
     <row r="33" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A33" s="43" t="str">
+      <c r="A33" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tab 7</v>
       </c>
-      <c r="B33" s="44">
+      <c r="B33" s="43">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="C33" s="44">
+      <c r="C33" s="43">
         <f t="shared" si="2"/>
         <v>55</v>
       </c>
-      <c r="D33" s="44">
+      <c r="D33" s="43">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="E33" s="44">
+      <c r="E33" s="43">
         <f t="shared" si="3"/>
         <v>55</v>
       </c>
-      <c r="F33" s="44">
+      <c r="F33" s="43">
         <f t="shared" si="3"/>
         <v>52.5</v>
       </c>
-      <c r="G33" s="46">
+      <c r="G33" s="45">
         <f t="shared" si="3"/>
         <v>85</v>
       </c>
       <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A34" s="43" t="str">
+      <c r="A34" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tab 8</v>
       </c>
-      <c r="B34" s="44">
+      <c r="B34" s="43">
         <f t="shared" si="2"/>
         <v>27.5</v>
       </c>
-      <c r="C34" s="44">
+      <c r="C34" s="43">
         <f t="shared" si="2"/>
         <v>52.5</v>
       </c>
-      <c r="D34" s="44">
+      <c r="D34" s="43">
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
-      <c r="E34" s="44">
+      <c r="E34" s="43">
         <f t="shared" si="3"/>
         <v>85</v>
       </c>
-      <c r="F34" s="44">
+      <c r="F34" s="43">
         <f t="shared" si="3"/>
         <v>27.5</v>
       </c>
-      <c r="G34" s="46">
+      <c r="G34" s="45">
         <f t="shared" si="3"/>
         <v>57.5</v>
       </c>
       <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A35" s="43" t="str">
+      <c r="A35" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tab 9</v>
       </c>
-      <c r="B35" s="44">
+      <c r="B35" s="43">
         <f t="shared" si="2"/>
         <v>47.5</v>
       </c>
-      <c r="C35" s="44">
+      <c r="C35" s="43">
         <f t="shared" si="2"/>
         <v>47.5</v>
       </c>
-      <c r="D35" s="44">
+      <c r="D35" s="43">
         <f t="shared" si="1"/>
         <v>42.5</v>
       </c>
-      <c r="E35" s="44">
+      <c r="E35" s="43">
         <f t="shared" si="3"/>
         <v>47.5</v>
       </c>
-      <c r="F35" s="44">
+      <c r="F35" s="43">
         <f t="shared" si="3"/>
         <v>27.5</v>
       </c>
-      <c r="G35" s="46">
+      <c r="G35" s="45">
         <f t="shared" si="3"/>
         <v>140</v>
       </c>
       <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A36" s="43" t="str">
+      <c r="A36" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tab 10</v>
       </c>
-      <c r="B36" s="44">
+      <c r="B36" s="43">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="C36" s="44">
+      <c r="C36" s="43">
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
-      <c r="D36" s="44">
+      <c r="D36" s="43">
         <f t="shared" si="1"/>
         <v>57.5</v>
       </c>
-      <c r="E36" s="44">
+      <c r="E36" s="43">
         <f t="shared" si="3"/>
         <v>45</v>
       </c>
-      <c r="F36" s="44">
+      <c r="F36" s="43">
         <f t="shared" si="3"/>
         <v>52.5</v>
       </c>
-      <c r="G36" s="46">
+      <c r="G36" s="45">
         <f t="shared" si="3"/>
         <v>57.5</v>
       </c>
       <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A37" s="43" t="str">
+      <c r="A37" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tab 11</v>
       </c>
-      <c r="B37" s="44">
+      <c r="B37" s="43">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="C37" s="44">
+      <c r="C37" s="43">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="D37" s="44">
+      <c r="D37" s="43">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E37" s="44">
+      <c r="E37" s="43">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="F37" s="44">
+      <c r="F37" s="43">
         <f t="shared" si="3"/>
         <v>55</v>
       </c>
-      <c r="G37" s="46">
+      <c r="G37" s="45">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:10" ht="15.95" customHeight="1" thickBot="1">
-      <c r="A38" s="47" t="str">
+      <c r="A38" s="46" t="str">
         <f t="shared" si="0"/>
         <v>Tab 12</v>
       </c>
-      <c r="B38" s="48">
+      <c r="B38" s="47">
         <f t="shared" si="2"/>
         <v>52.5</v>
       </c>
-      <c r="C38" s="49">
+      <c r="C38" s="48">
         <f t="shared" si="2"/>
         <v>52.5</v>
       </c>
-      <c r="D38" s="49">
+      <c r="D38" s="48">
         <f t="shared" si="1"/>
         <v>52.5</v>
       </c>
-      <c r="E38" s="49">
+      <c r="E38" s="48">
         <f t="shared" si="3"/>
         <v>52.5</v>
       </c>
-      <c r="F38" s="49">
+      <c r="F38" s="48">
         <f t="shared" si="3"/>
         <v>275</v>
       </c>
-      <c r="G38" s="50">
+      <c r="G38" s="49">
         <f t="shared" si="3"/>
         <v>27.5</v>
       </c>
       <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="44"/>
-      <c r="B39" s="44"/>
-      <c r="C39" s="44"/>
-      <c r="D39" s="44"/>
-      <c r="E39" s="44"/>
-      <c r="F39" s="44"/>
-      <c r="G39" s="44"/>
+      <c r="A39" s="43"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
       <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:10" ht="15.95" customHeight="1" thickBot="1">
-      <c r="A40" s="59" t="s">
+      <c r="A40" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="B40" s="60">
+      <c r="B40" s="59">
         <f t="shared" ref="B40:G40" si="4">AVERAGE(B$27:B$38)</f>
         <v>30.347222222222218</v>
       </c>
-      <c r="C40" s="61">
+      <c r="C40" s="60">
         <f t="shared" si="4"/>
         <v>56.666666666666664</v>
       </c>
-      <c r="D40" s="61">
+      <c r="D40" s="60">
         <f t="shared" si="4"/>
         <v>68.541666666666671</v>
       </c>
-      <c r="E40" s="61">
+      <c r="E40" s="60">
         <f t="shared" si="4"/>
         <v>60.277777777777771</v>
       </c>
-      <c r="F40" s="61">
+      <c r="F40" s="60">
         <f t="shared" si="4"/>
         <v>96.458333333333329</v>
       </c>
-      <c r="G40" s="62">
+      <c r="G40" s="61">
         <f t="shared" si="4"/>
         <v>53.055555555555564</v>
       </c>
@@ -2427,74 +2425,74 @@
       <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A42" s="69" t="s">
+      <c r="A42" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="B42" s="70"/>
-      <c r="C42" s="70"/>
-      <c r="D42" s="70"/>
-      <c r="E42" s="70"/>
-      <c r="F42" s="70"/>
-      <c r="G42" s="70"/>
+      <c r="B42" s="69"/>
+      <c r="C42" s="69"/>
+      <c r="D42" s="69"/>
+      <c r="E42" s="69"/>
+      <c r="F42" s="69"/>
+      <c r="G42" s="69"/>
       <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:10" ht="15.6" customHeight="1">
-      <c r="A43" s="69" t="s">
+      <c r="A43" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="B43" s="70"/>
-      <c r="C43" s="70"/>
-      <c r="D43" s="70"/>
-      <c r="E43" s="70"/>
-      <c r="F43" s="70"/>
-      <c r="G43" s="70"/>
+      <c r="B43" s="69"/>
+      <c r="C43" s="69"/>
+      <c r="D43" s="69"/>
+      <c r="E43" s="69"/>
+      <c r="F43" s="69"/>
+      <c r="G43" s="69"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="69" t="s">
+      <c r="A44" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="70"/>
-      <c r="C44" s="70"/>
-      <c r="D44" s="70"/>
-      <c r="E44" s="70"/>
-      <c r="F44" s="70"/>
-      <c r="G44" s="70"/>
+      <c r="B44" s="69"/>
+      <c r="C44" s="69"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="69"/>
+      <c r="G44" s="69"/>
     </row>
     <row r="45" spans="1:10" ht="15" customHeight="1">
-      <c r="A45" s="69" t="s">
+      <c r="A45" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="B45" s="70"/>
-      <c r="C45" s="70"/>
-      <c r="D45" s="70"/>
-      <c r="E45" s="70"/>
-      <c r="F45" s="70"/>
-      <c r="G45" s="70"/>
+      <c r="B45" s="69"/>
+      <c r="C45" s="69"/>
+      <c r="D45" s="69"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="69"/>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1">
-      <c r="A46" s="69" t="s">
+      <c r="A46" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="B46" s="70"/>
-      <c r="C46" s="70"/>
-      <c r="D46" s="70"/>
-      <c r="E46" s="70"/>
-      <c r="F46" s="70"/>
-      <c r="G46" s="70"/>
+      <c r="B46" s="69"/>
+      <c r="C46" s="69"/>
+      <c r="D46" s="69"/>
+      <c r="E46" s="69"/>
+      <c r="F46" s="69"/>
+      <c r="G46" s="69"/>
     </row>
     <row r="47" spans="1:10" ht="15" customHeight="1">
-      <c r="A47" s="69" t="s">
+      <c r="A47" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="B47" s="70"/>
-      <c r="C47" s="70"/>
-      <c r="D47" s="70"/>
-      <c r="E47" s="70"/>
-      <c r="F47" s="70"/>
-      <c r="G47" s="70"/>
+      <c r="B47" s="69"/>
+      <c r="C47" s="69"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="69"/>
+      <c r="F47" s="69"/>
+      <c r="G47" s="69"/>
     </row>
     <row r="48" spans="1:10" ht="15" customHeight="1"/>
     <row r="49" ht="15" customHeight="1"/>
@@ -2511,9 +2509,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
@@ -2522,15 +2520,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="23.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
     </row>
     <row r="2" spans="1:7" ht="14.25">
       <c r="A2" s="3"/>
@@ -2601,287 +2599,287 @@
       <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="76"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="76"/>
-      <c r="F8" s="76"/>
-      <c r="G8" s="77"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="74"/>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1" thickBot="1">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="33">
         <v>1</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="34">
         <v>2</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="34">
         <v>3</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="35">
         <v>4</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="34">
         <v>5</v>
       </c>
-      <c r="G9" s="37">
+      <c r="G9" s="36">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="20">
         <v>25</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="20">
         <v>34</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="20">
         <f>D11</f>
         <v>45</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="20">
         <v>34</v>
       </c>
-      <c r="F10" s="63">
+      <c r="F10" s="62">
         <v>56</v>
       </c>
-      <c r="G10" s="63"/>
+      <c r="G10" s="62"/>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="23">
         <v>12</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="23">
         <v>14</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="23">
         <v>45</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="23">
         <v>16</v>
       </c>
-      <c r="F11" s="64">
+      <c r="F11" s="63">
         <v>56</v>
       </c>
-      <c r="G11" s="64"/>
+      <c r="G11" s="63"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="23">
         <v>14</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="23">
         <v>34</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="23">
         <v>22</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="23">
         <v>14</v>
       </c>
-      <c r="F12" s="64">
+      <c r="F12" s="63">
         <v>21</v>
       </c>
-      <c r="G12" s="64"/>
+      <c r="G12" s="63"/>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1">
-      <c r="A13" s="33" t="s">
+      <c r="A13" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="23">
         <v>15</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="23">
         <v>15</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="23">
         <v>26</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="23">
         <v>43</v>
       </c>
-      <c r="F13" s="64">
+      <c r="F13" s="63">
         <v>15</v>
       </c>
-      <c r="G13" s="64"/>
+      <c r="G13" s="63"/>
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1">
-      <c r="A14" s="33" t="s">
+      <c r="A14" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24">
+      <c r="B14" s="23"/>
+      <c r="C14" s="23">
         <v>17</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="23">
         <v>17</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="23">
         <v>18</v>
       </c>
-      <c r="F14" s="64">
+      <c r="F14" s="63">
         <v>35</v>
       </c>
-      <c r="G14" s="64"/>
+      <c r="G14" s="63"/>
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1">
-      <c r="A15" s="33" t="s">
+      <c r="A15" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="23">
         <v>19</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="23">
         <v>33</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="23">
         <v>45</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="23">
         <v>19</v>
       </c>
-      <c r="F15" s="64">
+      <c r="F15" s="63">
         <f>SUM(F10:F11)</f>
         <v>112</v>
       </c>
-      <c r="G15" s="64"/>
+      <c r="G15" s="63"/>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1">
-      <c r="A16" s="33" t="s">
+      <c r="A16" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24">
+      <c r="B16" s="23"/>
+      <c r="C16" s="23">
         <v>22</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="23">
         <v>32</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="23">
         <v>22</v>
       </c>
-      <c r="F16" s="64">
+      <c r="F16" s="63">
         <v>21</v>
       </c>
-      <c r="G16" s="64"/>
+      <c r="G16" s="63"/>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1">
-      <c r="A17" s="33" t="s">
+      <c r="A17" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B17" s="23">
         <v>11</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="23">
         <v>21</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="23">
         <v>36</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="23">
         <v>34</v>
       </c>
-      <c r="F17" s="64">
+      <c r="F17" s="63">
         <v>11</v>
       </c>
-      <c r="G17" s="64"/>
+      <c r="G17" s="63"/>
     </row>
     <row r="18" spans="1:7" ht="15" customHeight="1">
-      <c r="A18" s="33" t="s">
+      <c r="A18" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="24">
+      <c r="B18" s="23">
         <v>19</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="23">
         <v>19</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="23">
         <v>17</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="23">
         <v>19</v>
       </c>
-      <c r="F18" s="64">
+      <c r="F18" s="63">
         <v>11</v>
       </c>
-      <c r="G18" s="64"/>
+      <c r="G18" s="63"/>
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1">
-      <c r="A19" s="33" t="s">
+      <c r="A19" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24">
+      <c r="B19" s="23"/>
+      <c r="C19" s="23">
         <v>34</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="23">
         <v>23</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="23">
         <v>18</v>
       </c>
-      <c r="F19" s="64">
+      <c r="F19" s="63">
         <v>21</v>
       </c>
-      <c r="G19" s="64"/>
+      <c r="G19" s="63"/>
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1">
-      <c r="A20" s="33" t="s">
+      <c r="A20" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B20" s="23">
         <v>20</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="23">
         <v>20</v>
       </c>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24">
+      <c r="D20" s="23"/>
+      <c r="E20" s="23">
         <v>20</v>
       </c>
-      <c r="F20" s="64">
+      <c r="F20" s="63">
         <v>22</v>
       </c>
-      <c r="G20" s="64"/>
+      <c r="G20" s="63"/>
     </row>
     <row r="21" spans="1:7" ht="15" customHeight="1" thickBot="1">
-      <c r="A21" s="33" t="s">
+      <c r="A21" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="24">
         <v>21</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="24">
         <v>21</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="24">
         <v>21</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="24">
         <v>21</v>
       </c>
-      <c r="F21" s="65">
+      <c r="F21" s="64">
         <f>SUM(G18:G21)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="65"/>
+      <c r="G21" s="64"/>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1">
       <c r="A22" s="3"/>
@@ -2893,577 +2891,517 @@
       <c r="G22" s="3"/>
     </row>
     <row r="23" spans="1:7" ht="15" customHeight="1" thickBot="1">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
     </row>
     <row r="24" spans="1:7" ht="15" customHeight="1" thickBot="1">
-      <c r="A24" s="38"/>
-      <c r="B24" s="78" t="s">
+      <c r="A24" s="37"/>
+      <c r="B24" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="79"/>
-      <c r="D24" s="79"/>
-      <c r="E24" s="79"/>
-      <c r="F24" s="79"/>
-      <c r="G24" s="80"/>
+      <c r="C24" s="76"/>
+      <c r="D24" s="76"/>
+      <c r="E24" s="76"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="77"/>
     </row>
     <row r="25" spans="1:7" ht="15" customHeight="1" thickBot="1">
-      <c r="A25" s="66"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67"/>
-      <c r="F25" s="67"/>
-      <c r="G25" s="68"/>
+      <c r="A25" s="65"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="66"/>
+      <c r="E25" s="66"/>
+      <c r="F25" s="66"/>
+      <c r="G25" s="67"/>
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1" thickBot="1">
-      <c r="A26" s="39" t="s">
+      <c r="A26" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="40">
+      <c r="B26" s="39">
         <f>B9</f>
         <v>1</v>
       </c>
-      <c r="C26" s="41">
+      <c r="C26" s="40">
         <f>C9</f>
         <v>2</v>
       </c>
-      <c r="D26" s="41">
+      <c r="D26" s="40">
         <f>D9</f>
         <v>3</v>
       </c>
-      <c r="E26" s="41">
+      <c r="E26" s="40">
         <v>4</v>
       </c>
-      <c r="F26" s="41">
+      <c r="F26" s="40">
         <f>F9</f>
         <v>5</v>
       </c>
-      <c r="G26" s="42">
+      <c r="G26" s="41">
         <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" customHeight="1">
-      <c r="A27" s="43" t="str">
+      <c r="A27" s="42" t="str">
         <f t="shared" ref="A27:A38" si="0">A10</f>
         <v>Tab 1</v>
       </c>
-      <c r="B27" s="44">
+      <c r="B27" s="43">
         <f>B10*$G$3*$G$4/75</f>
         <v>83.333333333333329</v>
       </c>
-      <c r="C27" s="44">
+      <c r="C27" s="43">
         <v>55</v>
       </c>
-      <c r="D27" s="44">
+      <c r="D27" s="43">
         <f t="shared" ref="D27:G38" si="1">D10*$G$3*$G$4/100</f>
         <v>112.5</v>
       </c>
-      <c r="E27" s="44">
+      <c r="E27" s="43">
         <f>E10*$G$3*$G$4/75</f>
         <v>113.33333333333333</v>
       </c>
-      <c r="F27" s="44">
+      <c r="F27" s="43">
         <f>F10*$G$3*$G$4/200</f>
         <v>70</v>
       </c>
-      <c r="G27" s="45">
+      <c r="G27" s="44">
         <f>G10*$G$3*$G$4/75</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1">
-      <c r="A28" s="43" t="str">
+      <c r="A28" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tab 2</v>
       </c>
-      <c r="B28" s="44">
+      <c r="B28" s="43">
         <f t="shared" ref="B28:C38" si="2">B11*$G$3*$G$4/100</f>
         <v>30</v>
       </c>
-      <c r="C28" s="44">
+      <c r="C28" s="43">
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="D28" s="44">
+      <c r="D28" s="43">
         <f t="shared" si="1"/>
         <v>112.5</v>
       </c>
-      <c r="E28" s="44">
+      <c r="E28" s="43">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="F28" s="44">
+      <c r="F28" s="43">
         <f t="shared" si="1"/>
         <v>140</v>
       </c>
-      <c r="G28" s="46">
+      <c r="G28" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1">
-      <c r="A29" s="43" t="str">
+      <c r="A29" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tab 3</v>
       </c>
-      <c r="B29" s="44">
+      <c r="B29" s="43">
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="C29" s="44">
+      <c r="C29" s="43">
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
-      <c r="D29" s="44">
+      <c r="D29" s="43">
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
-      <c r="E29" s="44">
+      <c r="E29" s="43">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="F29" s="44">
+      <c r="F29" s="43">
         <f t="shared" si="1"/>
         <v>52.5</v>
       </c>
-      <c r="G29" s="46">
+      <c r="G29" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15" customHeight="1">
-      <c r="A30" s="43" t="str">
+      <c r="A30" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tab 4</v>
       </c>
-      <c r="B30" s="44">
+      <c r="B30" s="43">
         <f t="shared" si="2"/>
         <v>37.5</v>
       </c>
-      <c r="C30" s="44">
+      <c r="C30" s="43">
         <f t="shared" si="2"/>
         <v>37.5</v>
       </c>
-      <c r="D30" s="44">
+      <c r="D30" s="43">
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
-      <c r="E30" s="44">
+      <c r="E30" s="43">
         <f t="shared" si="1"/>
         <v>107.5</v>
       </c>
-      <c r="F30" s="44">
+      <c r="F30" s="43">
         <f t="shared" si="1"/>
         <v>37.5</v>
       </c>
-      <c r="G30" s="46">
+      <c r="G30" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" customHeight="1">
-      <c r="A31" s="43" t="str">
+      <c r="A31" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tab 5</v>
       </c>
-      <c r="B31" s="44">
+      <c r="B31" s="43">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="C31" s="44">
+      <c r="C31" s="43">
         <f t="shared" si="2"/>
         <v>42.5</v>
       </c>
-      <c r="D31" s="44">
+      <c r="D31" s="43">
         <f t="shared" si="1"/>
         <v>42.5</v>
       </c>
-      <c r="E31" s="44">
+      <c r="E31" s="43">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="F31" s="44">
+      <c r="F31" s="43">
         <f t="shared" si="1"/>
         <v>87.5</v>
       </c>
-      <c r="G31" s="46">
+      <c r="G31" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" customHeight="1">
-      <c r="A32" s="43" t="str">
+      <c r="A32" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tab 6</v>
       </c>
-      <c r="B32" s="44">
+      <c r="B32" s="43">
         <f t="shared" si="2"/>
         <v>47.5</v>
       </c>
-      <c r="C32" s="44">
+      <c r="C32" s="43">
         <f t="shared" si="2"/>
         <v>82.5</v>
       </c>
-      <c r="D32" s="44">
+      <c r="D32" s="43">
         <f t="shared" si="1"/>
         <v>112.5</v>
       </c>
-      <c r="E32" s="44">
+      <c r="E32" s="43">
         <f t="shared" si="1"/>
         <v>47.5</v>
       </c>
-      <c r="F32" s="44">
+      <c r="F32" s="43">
         <f t="shared" si="1"/>
         <v>280</v>
       </c>
-      <c r="G32" s="46">
+      <c r="G32" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" customHeight="1">
-      <c r="A33" s="43" t="str">
+      <c r="A33" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tab 7</v>
       </c>
-      <c r="B33" s="44">
+      <c r="B33" s="43">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="C33" s="44">
+      <c r="C33" s="43">
         <f t="shared" si="2"/>
         <v>55</v>
       </c>
-      <c r="D33" s="44">
+      <c r="D33" s="43">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="E33" s="44">
+      <c r="E33" s="43">
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
-      <c r="F33" s="44">
+      <c r="F33" s="43">
         <f t="shared" si="1"/>
         <v>52.5</v>
       </c>
-      <c r="G33" s="46">
+      <c r="G33" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1">
-      <c r="A34" s="43" t="str">
+      <c r="A34" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tab 8</v>
       </c>
-      <c r="B34" s="44">
+      <c r="B34" s="43">
         <f t="shared" si="2"/>
         <v>27.5</v>
       </c>
-      <c r="C34" s="44">
+      <c r="C34" s="43">
         <f t="shared" si="2"/>
         <v>52.5</v>
       </c>
-      <c r="D34" s="44">
+      <c r="D34" s="43">
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
-      <c r="E34" s="44">
+      <c r="E34" s="43">
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
-      <c r="F34" s="44">
+      <c r="F34" s="43">
         <f t="shared" si="1"/>
         <v>27.5</v>
       </c>
-      <c r="G34" s="46">
+      <c r="G34" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" customHeight="1">
-      <c r="A35" s="43" t="str">
+      <c r="A35" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tab 9</v>
       </c>
-      <c r="B35" s="44">
+      <c r="B35" s="43">
         <f t="shared" si="2"/>
         <v>47.5</v>
       </c>
-      <c r="C35" s="44">
+      <c r="C35" s="43">
         <f t="shared" si="2"/>
         <v>47.5</v>
       </c>
-      <c r="D35" s="44">
+      <c r="D35" s="43">
         <f t="shared" si="1"/>
         <v>42.5</v>
       </c>
-      <c r="E35" s="44">
+      <c r="E35" s="43">
         <f t="shared" si="1"/>
         <v>47.5</v>
       </c>
-      <c r="F35" s="44">
+      <c r="F35" s="43">
         <f t="shared" si="1"/>
         <v>27.5</v>
       </c>
-      <c r="G35" s="46">
+      <c r="G35" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" customHeight="1">
-      <c r="A36" s="43" t="str">
+      <c r="A36" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tab 10</v>
       </c>
-      <c r="B36" s="44">
+      <c r="B36" s="43">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="C36" s="44">
+      <c r="C36" s="43">
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
-      <c r="D36" s="44">
+      <c r="D36" s="43">
         <f t="shared" si="1"/>
         <v>57.5</v>
       </c>
-      <c r="E36" s="44">
+      <c r="E36" s="43">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="F36" s="44">
+      <c r="F36" s="43">
         <f t="shared" si="1"/>
         <v>52.5</v>
       </c>
-      <c r="G36" s="46">
+      <c r="G36" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" customHeight="1">
-      <c r="A37" s="43" t="str">
+      <c r="A37" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Tab 11</v>
       </c>
-      <c r="B37" s="44">
+      <c r="B37" s="43">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="C37" s="44">
+      <c r="C37" s="43">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="D37" s="44">
+      <c r="D37" s="43">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E37" s="44">
+      <c r="E37" s="43">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="F37" s="44">
+      <c r="F37" s="43">
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
-      <c r="G37" s="46">
+      <c r="G37" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15" customHeight="1" thickBot="1">
-      <c r="A38" s="47" t="str">
+      <c r="A38" s="46" t="str">
         <f t="shared" si="0"/>
         <v>Tab 12</v>
       </c>
-      <c r="B38" s="48">
+      <c r="B38" s="47">
         <f t="shared" si="2"/>
         <v>52.5</v>
       </c>
-      <c r="C38" s="49">
+      <c r="C38" s="48">
         <f t="shared" si="2"/>
         <v>52.5</v>
       </c>
-      <c r="D38" s="49">
+      <c r="D38" s="48">
         <f t="shared" si="1"/>
         <v>52.5</v>
       </c>
-      <c r="E38" s="49">
+      <c r="E38" s="48">
         <f t="shared" si="1"/>
         <v>52.5</v>
       </c>
-      <c r="F38" s="49">
+      <c r="F38" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G38" s="50">
+      <c r="G38" s="49">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15" customHeight="1" thickBot="1">
-      <c r="A39" s="44"/>
-      <c r="B39" s="44"/>
-      <c r="C39" s="44"/>
-      <c r="D39" s="44"/>
-      <c r="E39" s="44"/>
-      <c r="F39" s="44"/>
-      <c r="G39" s="44"/>
+      <c r="A39" s="43"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
     </row>
     <row r="40" spans="1:7" ht="15" customHeight="1">
-      <c r="A40" s="51" t="s">
+      <c r="A40" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="52">
+      <c r="B40" s="51">
         <f t="shared" ref="B40:G40" si="3">MIN(B$27:B$38)</f>
         <v>0</v>
       </c>
-      <c r="C40" s="53">
+      <c r="C40" s="52">
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="D40" s="53">
+      <c r="D40" s="52">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E40" s="53">
+      <c r="E40" s="52">
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="F40" s="53">
+      <c r="F40" s="52">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G40" s="54">
+      <c r="G40" s="53">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" customHeight="1">
-      <c r="A41" s="55" t="s">
+      <c r="A41" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="56">
+      <c r="B41" s="55">
         <f t="shared" ref="B41:G41" si="4">MAX(B$27:B$38)</f>
         <v>83.333333333333329</v>
       </c>
-      <c r="C41" s="57">
+      <c r="C41" s="56">
         <f t="shared" si="4"/>
         <v>85</v>
       </c>
-      <c r="D41" s="57">
+      <c r="D41" s="56">
         <f t="shared" si="4"/>
         <v>112.5</v>
       </c>
-      <c r="E41" s="57">
+      <c r="E41" s="56">
         <f t="shared" si="4"/>
         <v>113.33333333333333</v>
       </c>
-      <c r="F41" s="57">
+      <c r="F41" s="56">
         <f t="shared" si="4"/>
         <v>280</v>
       </c>
-      <c r="G41" s="58">
+      <c r="G41" s="57">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15" customHeight="1" thickBot="1">
-      <c r="A42" s="59" t="s">
+      <c r="A42" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="B42" s="60">
+      <c r="B42" s="59">
         <f t="shared" ref="B42:G42" si="5">AVERAGE(B$27:B$38)</f>
         <v>34.236111111111107</v>
       </c>
-      <c r="C42" s="61">
+      <c r="C42" s="60">
         <f t="shared" si="5"/>
         <v>56.666666666666664</v>
       </c>
-      <c r="D42" s="61">
+      <c r="D42" s="60">
         <f t="shared" si="5"/>
         <v>68.541666666666671</v>
       </c>
-      <c r="E42" s="61">
+      <c r="E42" s="60">
         <f t="shared" si="5"/>
         <v>60.277777777777771</v>
       </c>
-      <c r="F42" s="61">
+      <c r="F42" s="60">
         <f t="shared" si="5"/>
         <v>73.541666666666671</v>
       </c>
-      <c r="G42" s="62">
+      <c r="G42" s="61">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" ht="15" customHeight="1">
-      <c r="A44" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="B44" s="72"/>
-      <c r="C44" s="72"/>
-      <c r="D44" s="72"/>
-      <c r="E44" s="72"/>
-      <c r="F44" s="72"/>
-    </row>
-    <row r="45" spans="1:7" ht="15" customHeight="1">
-      <c r="A45" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="B45" s="72"/>
-      <c r="C45" s="72"/>
-      <c r="D45" s="72"/>
-      <c r="E45" s="72"/>
-      <c r="F45" s="72"/>
-    </row>
-    <row r="46" spans="1:7" ht="15" customHeight="1">
-      <c r="A46" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="B46" s="72"/>
-      <c r="C46" s="72"/>
-      <c r="D46" s="72"/>
-      <c r="E46" s="72"/>
-      <c r="F46" s="72"/>
-    </row>
-    <row r="47" spans="1:7" ht="15" customHeight="1">
-      <c r="A47" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="B47" s="72"/>
-      <c r="C47" s="72"/>
-      <c r="D47" s="72"/>
-      <c r="E47" s="72"/>
-      <c r="F47" s="72"/>
-    </row>
-    <row r="48" spans="1:7" ht="15" customHeight="1">
-      <c r="A48" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="B48" s="72"/>
-      <c r="C48" s="72"/>
-      <c r="D48" s="72"/>
-      <c r="E48" s="72"/>
-      <c r="F48" s="72"/>
-    </row>
-    <row r="49" spans="1:6" ht="15" customHeight="1">
-      <c r="A49" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="B49" s="72"/>
-      <c r="C49" s="72"/>
-      <c r="D49" s="72"/>
-      <c r="E49" s="72"/>
-      <c r="F49" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="3">
